--- a/data/raw/Kawak/2025.xlsx
+++ b/data/raw/Kawak/2025.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Consolidado Indicadores/Data/raw/Kawak/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Indicadores_Oportunidad_Mejora/data/raw/Kawak/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{2553D8ED-1A7D-4653-A81C-B563898AD95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{416C4500-47E8-4C27-914A-257A6DBC2FE3}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{2553D8ED-1A7D-4653-A81C-B563898AD95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9034F534-9D69-49FA-A187-A73F1C9A7441}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0ABA65E9-32CA-4FC8-8179-9B0EBD2C31C1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{0ABA65E9-32CA-4FC8-8179-9B0EBD2C31C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Worksheet!$A$1:$Y$787</definedName>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12429" uniqueCount="1171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12430" uniqueCount="1171">
   <si>
     <t>Id</t>
   </si>
@@ -4026,7 +4027,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69DEF77A-E506-4471-8935-B3BC88D629C9}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Y787"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4111,7 +4111,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>84</v>
       </c>
@@ -4181,7 +4181,7 @@
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
     </row>
-    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>85</v>
       </c>
@@ -4251,7 +4251,7 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
     </row>
-    <row r="4" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>87</v>
       </c>
@@ -4321,7 +4321,7 @@
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
     </row>
-    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>88</v>
       </c>
@@ -4391,7 +4391,7 @@
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
     </row>
-    <row r="6" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>89</v>
       </c>
@@ -4461,7 +4461,7 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
     </row>
-    <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>90</v>
       </c>
@@ -4531,7 +4531,7 @@
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
     </row>
-    <row r="8" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>91</v>
       </c>
@@ -4601,7 +4601,7 @@
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
     </row>
-    <row r="9" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>92</v>
       </c>
@@ -4671,7 +4671,7 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
     </row>
-    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>94</v>
       </c>
@@ -4741,7 +4741,7 @@
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
     </row>
-    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>100</v>
       </c>
@@ -4811,7 +4811,7 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
     </row>
-    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>104</v>
       </c>
@@ -4881,7 +4881,7 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
     </row>
-    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>106</v>
       </c>
@@ -4951,7 +4951,7 @@
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
     </row>
-    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>109</v>
       </c>
@@ -5018,7 +5018,7 @@
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
     </row>
-    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>112</v>
       </c>
@@ -5087,7 +5087,7 @@
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
     </row>
-    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>113</v>
       </c>
@@ -5156,7 +5156,7 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
     </row>
-    <row r="17" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>114</v>
       </c>
@@ -5225,7 +5225,7 @@
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
     </row>
-    <row r="18" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>115</v>
       </c>
@@ -5294,7 +5294,7 @@
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
     </row>
-    <row r="19" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>116</v>
       </c>
@@ -5355,7 +5355,7 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
     </row>
-    <row r="20" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>117</v>
       </c>
@@ -5424,7 +5424,7 @@
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
     </row>
-    <row r="21" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>118</v>
       </c>
@@ -5493,7 +5493,7 @@
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
     </row>
-    <row r="22" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>126</v>
       </c>
@@ -5563,7 +5563,7 @@
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
     </row>
-    <row r="23" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>127</v>
       </c>
@@ -5633,7 +5633,7 @@
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
     </row>
-    <row r="24" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>133</v>
       </c>
@@ -5700,7 +5700,7 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
     </row>
-    <row r="25" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>144</v>
       </c>
@@ -5764,7 +5764,7 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
     </row>
-    <row r="26" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>147</v>
       </c>
@@ -5824,7 +5824,7 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
     </row>
-    <row r="27" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>150</v>
       </c>
@@ -5887,7 +5887,7 @@
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
     </row>
-    <row r="28" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>151</v>
       </c>
@@ -5952,7 +5952,7 @@
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
     </row>
-    <row r="29" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>200</v>
       </c>
@@ -6014,7 +6014,7 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
     </row>
-    <row r="30" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>202</v>
       </c>
@@ -6072,7 +6072,7 @@
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
     </row>
-    <row r="31" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>206</v>
       </c>
@@ -6130,7 +6130,7 @@
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
     </row>
-    <row r="32" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>216</v>
       </c>
@@ -6204,7 +6204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>216</v>
       </c>
@@ -6278,7 +6278,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>216</v>
       </c>
@@ -6352,7 +6352,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>216</v>
       </c>
@@ -6426,7 +6426,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="36" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>216</v>
       </c>
@@ -6500,7 +6500,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="37" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>216</v>
       </c>
@@ -6574,7 +6574,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="38" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>216</v>
       </c>
@@ -6648,7 +6648,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>221</v>
       </c>
@@ -6712,7 +6712,7 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
     </row>
-    <row r="40" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>221</v>
       </c>
@@ -6786,7 +6786,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>221</v>
       </c>
@@ -6860,7 +6860,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="42" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>221</v>
       </c>
@@ -6934,7 +6934,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>221</v>
       </c>
@@ -7008,7 +7008,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="44" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>221</v>
       </c>
@@ -7082,7 +7082,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="45" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>221</v>
       </c>
@@ -7156,7 +7156,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>222</v>
       </c>
@@ -7230,7 +7230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>222</v>
       </c>
@@ -7304,7 +7304,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="48" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>223</v>
       </c>
@@ -7376,7 +7376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>223</v>
       </c>
@@ -7450,7 +7450,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="50" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>223</v>
       </c>
@@ -7524,7 +7524,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="51" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>224</v>
       </c>
@@ -7584,7 +7584,7 @@
       <c r="W51" s="3"/>
       <c r="X51" s="3"/>
     </row>
-    <row r="52" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>224</v>
       </c>
@@ -7658,7 +7658,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="53" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>224</v>
       </c>
@@ -7732,7 +7732,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="54" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>224</v>
       </c>
@@ -7806,7 +7806,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="55" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>224</v>
       </c>
@@ -7878,7 +7878,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="56" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>224</v>
       </c>
@@ -7952,7 +7952,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="57" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>224</v>
       </c>
@@ -8026,7 +8026,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="58" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>226</v>
       </c>
@@ -8098,7 +8098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>226</v>
       </c>
@@ -8172,7 +8172,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="60" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>226</v>
       </c>
@@ -8246,7 +8246,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>226</v>
       </c>
@@ -8320,7 +8320,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>226</v>
       </c>
@@ -8394,7 +8394,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="63" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>226</v>
       </c>
@@ -8468,7 +8468,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="64" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>226</v>
       </c>
@@ -8542,7 +8542,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="65" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>227</v>
       </c>
@@ -8614,7 +8614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>227</v>
       </c>
@@ -8688,7 +8688,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="67" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>227</v>
       </c>
@@ -8758,7 +8758,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="68" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>227</v>
       </c>
@@ -8832,7 +8832,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="69" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>227</v>
       </c>
@@ -8902,7 +8902,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="70" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>227</v>
       </c>
@@ -8972,7 +8972,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="71" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>227</v>
       </c>
@@ -9046,7 +9046,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="72" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>228</v>
       </c>
@@ -9118,7 +9118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>228</v>
       </c>
@@ -9192,7 +9192,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="74" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>228</v>
       </c>
@@ -9266,7 +9266,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="75" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>228</v>
       </c>
@@ -9340,7 +9340,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="76" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>228</v>
       </c>
@@ -9414,7 +9414,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="77" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>228</v>
       </c>
@@ -9488,7 +9488,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="78" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>228</v>
       </c>
@@ -9562,7 +9562,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="79" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>235</v>
       </c>
@@ -9619,7 +9619,7 @@
       <c r="X79" s="3"/>
       <c r="Y79" s="3"/>
     </row>
-    <row r="80" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>236</v>
       </c>
@@ -9675,7 +9675,7 @@
       <c r="W80" s="3"/>
       <c r="X80" s="3"/>
     </row>
-    <row r="81" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>244</v>
       </c>
@@ -9743,7 +9743,7 @@
       <c r="W81" s="3"/>
       <c r="X81" s="3"/>
     </row>
-    <row r="82" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>255</v>
       </c>
@@ -9805,7 +9805,7 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
     </row>
-    <row r="83" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>255</v>
       </c>
@@ -9879,7 +9879,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="84" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>255</v>
       </c>
@@ -9953,7 +9953,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="85" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>255</v>
       </c>
@@ -10027,7 +10027,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="86" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>255</v>
       </c>
@@ -10101,7 +10101,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="87" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>255</v>
       </c>
@@ -10175,7 +10175,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="88" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>255</v>
       </c>
@@ -10249,7 +10249,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="89" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>272</v>
       </c>
@@ -10311,7 +10311,7 @@
       <c r="W89" s="3"/>
       <c r="X89" s="3"/>
     </row>
-    <row r="90" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>288</v>
       </c>
@@ -10370,7 +10370,7 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
     </row>
-    <row r="91" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>318</v>
       </c>
@@ -10428,7 +10428,7 @@
       <c r="W91" s="3"/>
       <c r="X91" s="3"/>
     </row>
-    <row r="92" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>326</v>
       </c>
@@ -10486,7 +10486,7 @@
       <c r="W92" s="3"/>
       <c r="X92" s="3"/>
     </row>
-    <row r="93" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>334</v>
       </c>
@@ -10546,7 +10546,7 @@
       <c r="W93" s="3"/>
       <c r="X93" s="3"/>
     </row>
-    <row r="94" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>336</v>
       </c>
@@ -10602,7 +10602,7 @@
       <c r="W94" s="3"/>
       <c r="X94" s="3"/>
     </row>
-    <row r="95" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>339</v>
       </c>
@@ -10660,7 +10660,7 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
     </row>
-    <row r="96" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>346</v>
       </c>
@@ -10718,7 +10718,7 @@
       <c r="W96" s="3"/>
       <c r="X96" s="3"/>
     </row>
-    <row r="97" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>355</v>
       </c>
@@ -10774,7 +10774,7 @@
       <c r="W97" s="3"/>
       <c r="X97" s="3"/>
     </row>
-    <row r="98" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>361</v>
       </c>
@@ -10832,7 +10832,7 @@
       <c r="W98" s="3"/>
       <c r="X98" s="3"/>
     </row>
-    <row r="99" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>366</v>
       </c>
@@ -10890,7 +10890,7 @@
       <c r="W99" s="3"/>
       <c r="X99" s="3"/>
     </row>
-    <row r="100" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>367</v>
       </c>
@@ -10948,7 +10948,7 @@
       <c r="W100" s="3"/>
       <c r="X100" s="3"/>
     </row>
-    <row r="101" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>377</v>
       </c>
@@ -11006,7 +11006,7 @@
       <c r="W101" s="3"/>
       <c r="X101" s="3"/>
     </row>
-    <row r="102" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>392</v>
       </c>
@@ -11064,7 +11064,7 @@
       <c r="W102" s="3"/>
       <c r="X102" s="3"/>
     </row>
-    <row r="103" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>393</v>
       </c>
@@ -11120,7 +11120,7 @@
       <c r="W103" s="3"/>
       <c r="X103" s="3"/>
     </row>
-    <row r="104" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>402</v>
       </c>
@@ -11176,7 +11176,7 @@
       <c r="W104" s="3"/>
       <c r="X104" s="3"/>
     </row>
-    <row r="105" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>413</v>
       </c>
@@ -11232,7 +11232,7 @@
       <c r="W105" s="3"/>
       <c r="X105" s="3"/>
     </row>
-    <row r="106" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>423</v>
       </c>
@@ -11290,7 +11290,7 @@
       <c r="W106" s="3"/>
       <c r="X106" s="3"/>
     </row>
-    <row r="107" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>424</v>
       </c>
@@ -11348,7 +11348,7 @@
       <c r="W107" s="3"/>
       <c r="X107" s="3"/>
     </row>
-    <row r="108" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>437</v>
       </c>
@@ -11406,7 +11406,7 @@
       <c r="W108" s="3"/>
       <c r="X108" s="3"/>
     </row>
-    <row r="109" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>460</v>
       </c>
@@ -11462,7 +11462,7 @@
       <c r="W109" s="3"/>
       <c r="X109" s="3"/>
     </row>
-    <row r="110" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>487</v>
       </c>
@@ -11518,7 +11518,7 @@
       <c r="W110" s="3"/>
       <c r="X110" s="3"/>
     </row>
-    <row r="111" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>490</v>
       </c>
@@ -11574,7 +11574,7 @@
       <c r="W111" s="3"/>
       <c r="X111" s="3"/>
     </row>
-    <row r="112" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>491</v>
       </c>
@@ -11630,7 +11630,7 @@
       <c r="W112" s="3"/>
       <c r="X112" s="3"/>
     </row>
-    <row r="113" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>492</v>
       </c>
@@ -11686,7 +11686,7 @@
       <c r="W113" s="3"/>
       <c r="X113" s="3"/>
     </row>
-    <row r="114" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>493</v>
       </c>
@@ -11742,7 +11742,7 @@
       <c r="W114" s="3"/>
       <c r="X114" s="3"/>
     </row>
-    <row r="115" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>494</v>
       </c>
@@ -11798,7 +11798,7 @@
       <c r="W115" s="3"/>
       <c r="X115" s="3"/>
     </row>
-    <row r="116" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>495</v>
       </c>
@@ -11854,7 +11854,7 @@
       <c r="W116" s="3"/>
       <c r="X116" s="3"/>
     </row>
-    <row r="117" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>496</v>
       </c>
@@ -11910,7 +11910,7 @@
       <c r="W117" s="3"/>
       <c r="X117" s="3"/>
     </row>
-    <row r="118" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>497</v>
       </c>
@@ -11964,7 +11964,7 @@
       <c r="W118" s="3"/>
       <c r="X118" s="3"/>
     </row>
-    <row r="119" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>498</v>
       </c>
@@ -12020,7 +12020,7 @@
       <c r="W119" s="3"/>
       <c r="X119" s="3"/>
     </row>
-    <row r="120" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>499</v>
       </c>
@@ -12074,7 +12074,7 @@
       <c r="W120" s="3"/>
       <c r="X120" s="3"/>
     </row>
-    <row r="121" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>500</v>
       </c>
@@ -12130,7 +12130,7 @@
       <c r="W121" s="3"/>
       <c r="X121" s="3"/>
     </row>
-    <row r="122" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>501</v>
       </c>
@@ -12186,7 +12186,7 @@
       <c r="W122" s="3"/>
       <c r="X122" s="3"/>
     </row>
-    <row r="123" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>502</v>
       </c>
@@ -12242,7 +12242,7 @@
       <c r="W123" s="3"/>
       <c r="X123" s="3"/>
     </row>
-    <row r="124" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>503</v>
       </c>
@@ -12298,7 +12298,7 @@
       <c r="W124" s="3"/>
       <c r="X124" s="3"/>
     </row>
-    <row r="125" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>504</v>
       </c>
@@ -12354,7 +12354,7 @@
       <c r="W125" s="3"/>
       <c r="X125" s="3"/>
     </row>
-    <row r="126" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>505</v>
       </c>
@@ -12410,7 +12410,7 @@
       <c r="W126" s="3"/>
       <c r="X126" s="3"/>
     </row>
-    <row r="127" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>508</v>
       </c>
@@ -12466,7 +12466,7 @@
       <c r="W127" s="3"/>
       <c r="X127" s="3"/>
     </row>
-    <row r="128" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>522</v>
       </c>
@@ -12520,7 +12520,7 @@
       <c r="W128" s="3"/>
       <c r="X128" s="3"/>
     </row>
-    <row r="129" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>527</v>
       </c>
@@ -12572,7 +12572,7 @@
       <c r="W129" s="3"/>
       <c r="X129" s="3"/>
     </row>
-    <row r="130" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>528</v>
       </c>
@@ -12627,7 +12627,7 @@
       <c r="X130" s="3"/>
       <c r="Y130" s="3"/>
     </row>
-    <row r="131" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>541</v>
       </c>
@@ -12681,7 +12681,7 @@
       <c r="W131" s="3"/>
       <c r="X131" s="3"/>
     </row>
-    <row r="132" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>542</v>
       </c>
@@ -12745,7 +12745,7 @@
       <c r="W132" s="3"/>
       <c r="X132" s="3"/>
     </row>
-    <row r="133" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>542</v>
       </c>
@@ -12819,7 +12819,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="134" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>542</v>
       </c>
@@ -12893,7 +12893,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="135" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>542</v>
       </c>
@@ -12967,7 +12967,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="136" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>542</v>
       </c>
@@ -13041,7 +13041,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="137" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>546</v>
       </c>
@@ -13103,7 +13103,7 @@
       <c r="W137" s="3"/>
       <c r="X137" s="3"/>
     </row>
-    <row r="138" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>546</v>
       </c>
@@ -13174,7 +13174,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="139" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>546</v>
       </c>
@@ -13245,7 +13245,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="140" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>546</v>
       </c>
@@ -13316,7 +13316,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="141" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>547</v>
       </c>
@@ -13370,7 +13370,7 @@
       <c r="W141" s="3"/>
       <c r="X141" s="3"/>
     </row>
-    <row r="142" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>552</v>
       </c>
@@ -13424,7 +13424,7 @@
       <c r="W142" s="3"/>
       <c r="X142" s="3"/>
     </row>
-    <row r="143" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>553</v>
       </c>
@@ -13478,7 +13478,7 @@
       <c r="W143" s="3"/>
       <c r="X143" s="3"/>
     </row>
-    <row r="144" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>556</v>
       </c>
@@ -13532,7 +13532,7 @@
       <c r="W144" s="3"/>
       <c r="X144" s="3"/>
     </row>
-    <row r="145" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>290</v>
       </c>
@@ -13605,7 +13605,7 @@
         <v>91.666666666666657</v>
       </c>
     </row>
-    <row r="146" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>290</v>
       </c>
@@ -13679,7 +13679,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="147" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>290</v>
       </c>
@@ -13753,7 +13753,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="148" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>290</v>
       </c>
@@ -13827,7 +13827,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="149" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>290</v>
       </c>
@@ -13901,7 +13901,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="150" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>290</v>
       </c>
@@ -13975,7 +13975,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="151" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>290</v>
       </c>
@@ -14049,7 +14049,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="152" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>290</v>
       </c>
@@ -14123,7 +14123,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="153" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>290</v>
       </c>
@@ -14197,7 +14197,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="154" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>290</v>
       </c>
@@ -14271,7 +14271,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="155" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>77</v>
       </c>
@@ -14348,7 +14348,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="156" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>121</v>
       </c>
@@ -14425,7 +14425,7 @@
         <v>99.18</v>
       </c>
     </row>
-    <row r="157" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>122</v>
       </c>
@@ -14502,7 +14502,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="158" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>124</v>
       </c>
@@ -14579,7 +14579,7 @@
         <v>9.1157702825888781E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>125</v>
       </c>
@@ -14656,7 +14656,7 @@
         <v>0.27347310847766643</v>
       </c>
     </row>
-    <row r="160" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>128</v>
       </c>
@@ -14733,7 +14733,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="161" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>172</v>
       </c>
@@ -14810,7 +14810,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="162" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>208</v>
       </c>
@@ -14887,7 +14887,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="163" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>208</v>
       </c>
@@ -14964,7 +14964,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="164" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>208</v>
       </c>
@@ -15041,7 +15041,7 @@
         <v>249.5</v>
       </c>
     </row>
-    <row r="165" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>208</v>
       </c>
@@ -15118,7 +15118,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="166" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>208</v>
       </c>
@@ -15195,7 +15195,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="167" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>208</v>
       </c>
@@ -15272,7 +15272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>208</v>
       </c>
@@ -15349,7 +15349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>214</v>
       </c>
@@ -15426,7 +15426,7 @@
         <v>2054.7600000000002</v>
       </c>
     </row>
-    <row r="170" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>214</v>
       </c>
@@ -15503,7 +15503,7 @@
         <v>1130.94</v>
       </c>
     </row>
-    <row r="171" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>214</v>
       </c>
@@ -15580,7 +15580,7 @@
         <v>406.56</v>
       </c>
     </row>
-    <row r="172" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>214</v>
       </c>
@@ -15657,7 +15657,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="173" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>214</v>
       </c>
@@ -15734,7 +15734,7 @@
         <v>406.9</v>
       </c>
     </row>
-    <row r="174" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>214</v>
       </c>
@@ -15811,7 +15811,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="175" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>214</v>
       </c>
@@ -15888,7 +15888,7 @@
         <v>110.36</v>
       </c>
     </row>
-    <row r="176" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>217</v>
       </c>
@@ -15965,7 +15965,7 @@
         <v>139.19</v>
       </c>
     </row>
-    <row r="177" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>217</v>
       </c>
@@ -16042,7 +16042,7 @@
         <v>240.68</v>
       </c>
     </row>
-    <row r="178" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>217</v>
       </c>
@@ -16119,7 +16119,7 @@
         <v>19.850000000000001</v>
       </c>
     </row>
-    <row r="179" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>217</v>
       </c>
@@ -16196,7 +16196,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="180" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>217</v>
       </c>
@@ -16273,7 +16273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>217</v>
       </c>
@@ -16350,7 +16350,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="182" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>217</v>
       </c>
@@ -16427,7 +16427,7 @@
         <v>51.96</v>
       </c>
     </row>
-    <row r="183" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>218</v>
       </c>
@@ -16504,7 +16504,7 @@
         <v>113367.97</v>
       </c>
     </row>
-    <row r="184" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>218</v>
       </c>
@@ -16581,7 +16581,7 @@
         <v>54501</v>
       </c>
     </row>
-    <row r="185" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>218</v>
       </c>
@@ -16658,7 +16658,7 @@
         <v>42180</v>
       </c>
     </row>
-    <row r="186" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>218</v>
       </c>
@@ -16735,7 +16735,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="187" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>218</v>
       </c>
@@ -16812,7 +16812,7 @@
         <v>10775</v>
       </c>
     </row>
-    <row r="188" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>218</v>
       </c>
@@ -16889,7 +16889,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="189" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>218</v>
       </c>
@@ -16966,7 +16966,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="190" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>225</v>
       </c>
@@ -17041,7 +17041,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="191" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>225</v>
       </c>
@@ -17118,7 +17118,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="192" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>225</v>
       </c>
@@ -17193,7 +17193,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="193" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>225</v>
       </c>
@@ -17270,7 +17270,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="194" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>225</v>
       </c>
@@ -17347,7 +17347,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="195" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>225</v>
       </c>
@@ -17424,7 +17424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>225</v>
       </c>
@@ -17501,7 +17501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>239</v>
       </c>
@@ -17578,7 +17578,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="198" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>239</v>
       </c>
@@ -17655,7 +17655,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="199" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>239</v>
       </c>
@@ -17732,7 +17732,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="200" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>239</v>
       </c>
@@ -17807,7 +17807,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="201" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>239</v>
       </c>
@@ -17884,7 +17884,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="202" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>239</v>
       </c>
@@ -17961,7 +17961,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="203" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>241</v>
       </c>
@@ -18030,7 +18030,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="204" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>434</v>
       </c>
@@ -18105,7 +18105,7 @@
         <v>2072.4699999999998</v>
       </c>
     </row>
-    <row r="205" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>434</v>
       </c>
@@ -18182,7 +18182,7 @@
         <v>2071.7199999999998</v>
       </c>
     </row>
-    <row r="206" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>434</v>
       </c>
@@ -18259,7 +18259,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="207" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>434</v>
       </c>
@@ -18336,7 +18336,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="208" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>434</v>
       </c>
@@ -18413,7 +18413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>434</v>
       </c>
@@ -18490,7 +18490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>434</v>
       </c>
@@ -18567,7 +18567,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="211" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>436</v>
       </c>
@@ -18644,7 +18644,7 @@
         <v>9.1999999999999993</v>
       </c>
     </row>
-    <row r="212" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>436</v>
       </c>
@@ -18721,7 +18721,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="213" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>436</v>
       </c>
@@ -18798,7 +18798,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="214" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>485</v>
       </c>
@@ -18871,7 +18871,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="215" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>485</v>
       </c>
@@ -18943,7 +18943,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="216" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>485</v>
       </c>
@@ -19017,7 +19017,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="217" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>485</v>
       </c>
@@ -19091,7 +19091,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="218" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>485</v>
       </c>
@@ -19165,7 +19165,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="219" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>485</v>
       </c>
@@ -19239,7 +19239,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="220" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>485</v>
       </c>
@@ -19313,7 +19313,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="221" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>485</v>
       </c>
@@ -19387,7 +19387,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="222" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>485</v>
       </c>
@@ -19461,7 +19461,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>485</v>
       </c>
@@ -19535,7 +19535,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="224" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>488</v>
       </c>
@@ -19610,7 +19610,7 @@
         <v>78.048780487804876</v>
       </c>
     </row>
-    <row r="225" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>488</v>
       </c>
@@ -19684,7 +19684,7 @@
         <v>78.790000000000006</v>
       </c>
     </row>
-    <row r="226" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>488</v>
       </c>
@@ -19758,7 +19758,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="227" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>488</v>
       </c>
@@ -19832,7 +19832,7 @@
         <v>82.61</v>
       </c>
     </row>
-    <row r="228" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>488</v>
       </c>
@@ -19906,7 +19906,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="229" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>488</v>
       </c>
@@ -19980,7 +19980,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="230" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>488</v>
       </c>
@@ -20054,7 +20054,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="231" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>488</v>
       </c>
@@ -20128,7 +20128,7 @@
         <v>79.03</v>
       </c>
     </row>
-    <row r="232" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>488</v>
       </c>
@@ -20202,7 +20202,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="233" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>488</v>
       </c>
@@ -20276,7 +20276,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="234" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>509</v>
       </c>
@@ -20337,7 +20337,7 @@
         <v>99.45</v>
       </c>
     </row>
-    <row r="235" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>509</v>
       </c>
@@ -20411,7 +20411,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="236" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>509</v>
       </c>
@@ -20485,7 +20485,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="237" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>509</v>
       </c>
@@ -20559,7 +20559,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="238" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>509</v>
       </c>
@@ -20633,7 +20633,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="239" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>509</v>
       </c>
@@ -20707,7 +20707,7 @@
         <v>98.77</v>
       </c>
     </row>
-    <row r="240" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>509</v>
       </c>
@@ -20781,7 +20781,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="241" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>509</v>
       </c>
@@ -20855,7 +20855,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="242" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>509</v>
       </c>
@@ -20929,7 +20929,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="243" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>509</v>
       </c>
@@ -21003,7 +21003,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="244" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>509</v>
       </c>
@@ -21077,7 +21077,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="245" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>509</v>
       </c>
@@ -21151,7 +21151,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="246" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>509</v>
       </c>
@@ -21225,7 +21225,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="247" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>509</v>
       </c>
@@ -21299,7 +21299,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="248" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>509</v>
       </c>
@@ -21373,7 +21373,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="249" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>509</v>
       </c>
@@ -21447,7 +21447,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="250" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>509</v>
       </c>
@@ -21521,7 +21521,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="251" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>509</v>
       </c>
@@ -21595,7 +21595,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="252" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>509</v>
       </c>
@@ -21669,7 +21669,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="253" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>68</v>
       </c>
@@ -21744,7 +21744,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="254" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>73</v>
       </c>
@@ -21821,7 +21821,7 @@
         <v>18.41</v>
       </c>
     </row>
-    <row r="255" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>74</v>
       </c>
@@ -21898,7 +21898,7 @@
         <v>80.327868852459019</v>
       </c>
     </row>
-    <row r="256" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>86</v>
       </c>
@@ -21975,7 +21975,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="257" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>95</v>
       </c>
@@ -22052,7 +22052,7 @@
         <v>33.333333333333329</v>
       </c>
     </row>
-    <row r="258" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>143</v>
       </c>
@@ -22129,7 +22129,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="259" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>145</v>
       </c>
@@ -22206,7 +22206,7 @@
         <v>1.545454545454545</v>
       </c>
     </row>
-    <row r="260" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>146</v>
       </c>
@@ -22283,7 +22283,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="261" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>148</v>
       </c>
@@ -22360,7 +22360,7 @@
         <v>1.977873977873978</v>
       </c>
     </row>
-    <row r="262" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>159</v>
       </c>
@@ -22410,7 +22410,7 @@
         <v>97.8</v>
       </c>
     </row>
-    <row r="263" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>167</v>
       </c>
@@ -22481,7 +22481,7 @@
       <c r="X263" s="3"/>
       <c r="Y263" s="3"/>
     </row>
-    <row r="264" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>193</v>
       </c>
@@ -22546,7 +22546,7 @@
       <c r="X264" s="3"/>
       <c r="Y264" s="3"/>
     </row>
-    <row r="265" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>199</v>
       </c>
@@ -22615,7 +22615,7 @@
       <c r="X265" s="3"/>
       <c r="Y265" s="3"/>
     </row>
-    <row r="266" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
         <v>203</v>
       </c>
@@ -22692,7 +22692,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="267" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>203</v>
       </c>
@@ -22769,7 +22769,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="268" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>203</v>
       </c>
@@ -22846,7 +22846,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="269" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>203</v>
       </c>
@@ -22923,7 +22923,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="270" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>204</v>
       </c>
@@ -22988,7 +22988,7 @@
       <c r="X270" s="3"/>
       <c r="Y270" s="3"/>
     </row>
-    <row r="271" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>205</v>
       </c>
@@ -23053,7 +23053,7 @@
       <c r="X271" s="3"/>
       <c r="Y271" s="3"/>
     </row>
-    <row r="272" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>207</v>
       </c>
@@ -23118,7 +23118,7 @@
       <c r="X272" s="3"/>
       <c r="Y272" s="3"/>
     </row>
-    <row r="273" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
         <v>215</v>
       </c>
@@ -23195,7 +23195,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="274" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>215</v>
       </c>
@@ -23272,7 +23272,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="275" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>215</v>
       </c>
@@ -23349,7 +23349,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="276" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>215</v>
       </c>
@@ -23426,7 +23426,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="277" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>215</v>
       </c>
@@ -23503,7 +23503,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="278" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>215</v>
       </c>
@@ -23580,7 +23580,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="279" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>215</v>
       </c>
@@ -23657,7 +23657,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="280" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
         <v>219</v>
       </c>
@@ -23732,7 +23732,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="281" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>219</v>
       </c>
@@ -23809,7 +23809,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="282" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>219</v>
       </c>
@@ -23886,7 +23886,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="283" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>219</v>
       </c>
@@ -23963,7 +23963,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="284" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>219</v>
       </c>
@@ -24040,7 +24040,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="285" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>219</v>
       </c>
@@ -24117,7 +24117,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="286" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>219</v>
       </c>
@@ -24194,7 +24194,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="287" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>219</v>
       </c>
@@ -24252,7 +24252,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="288" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
         <v>220</v>
       </c>
@@ -24327,7 +24327,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="289" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>220</v>
       </c>
@@ -24404,7 +24404,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="290" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>220</v>
       </c>
@@ -24481,7 +24481,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="291" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>220</v>
       </c>
@@ -24558,7 +24558,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="292" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>220</v>
       </c>
@@ -24635,7 +24635,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="293" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>220</v>
       </c>
@@ -24708,7 +24708,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="294" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>220</v>
       </c>
@@ -24785,7 +24785,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="295" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>230</v>
       </c>
@@ -24848,7 +24848,7 @@
       <c r="X295" s="3"/>
       <c r="Y295" s="3"/>
     </row>
-    <row r="296" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>231</v>
       </c>
@@ -24911,7 +24911,7 @@
       <c r="X296" s="3"/>
       <c r="Y296" s="3"/>
     </row>
-    <row r="297" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>232</v>
       </c>
@@ -24974,7 +24974,7 @@
       <c r="X297" s="3"/>
       <c r="Y297" s="3"/>
     </row>
-    <row r="298" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>245</v>
       </c>
@@ -25039,7 +25039,7 @@
       <c r="X298" s="3"/>
       <c r="Y298" s="3"/>
     </row>
-    <row r="299" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>246</v>
       </c>
@@ -25102,7 +25102,7 @@
       <c r="X299" s="3"/>
       <c r="Y299" s="3"/>
     </row>
-    <row r="300" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>252</v>
       </c>
@@ -25167,7 +25167,7 @@
       <c r="X300" s="3"/>
       <c r="Y300" s="3"/>
     </row>
-    <row r="301" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>256</v>
       </c>
@@ -25230,7 +25230,7 @@
       <c r="X301" s="3"/>
       <c r="Y301" s="3"/>
     </row>
-    <row r="302" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>260</v>
       </c>
@@ -25295,7 +25295,7 @@
       <c r="X302" s="3"/>
       <c r="Y302" s="3"/>
     </row>
-    <row r="303" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>261</v>
       </c>
@@ -25360,7 +25360,7 @@
       <c r="X303" s="3"/>
       <c r="Y303" s="3"/>
     </row>
-    <row r="304" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>262</v>
       </c>
@@ -25423,7 +25423,7 @@
       <c r="X304" s="3"/>
       <c r="Y304" s="3"/>
     </row>
-    <row r="305" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>268</v>
       </c>
@@ -25488,7 +25488,7 @@
       <c r="X305" s="3"/>
       <c r="Y305" s="3"/>
     </row>
-    <row r="306" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>269</v>
       </c>
@@ -25553,7 +25553,7 @@
       <c r="X306" s="3"/>
       <c r="Y306" s="3"/>
     </row>
-    <row r="307" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>270</v>
       </c>
@@ -25618,7 +25618,7 @@
       <c r="X307" s="3"/>
       <c r="Y307" s="3"/>
     </row>
-    <row r="308" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>271</v>
       </c>
@@ -25683,7 +25683,7 @@
       <c r="X308" s="3"/>
       <c r="Y308" s="3"/>
     </row>
-    <row r="309" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>273</v>
       </c>
@@ -25748,7 +25748,7 @@
       <c r="X309" s="3"/>
       <c r="Y309" s="3"/>
     </row>
-    <row r="310" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
         <v>274</v>
       </c>
@@ -25825,7 +25825,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="311" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>274</v>
       </c>
@@ -25902,7 +25902,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="312" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>274</v>
       </c>
@@ -25979,7 +25979,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="313" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>274</v>
       </c>
@@ -26056,7 +26056,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="314" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>274</v>
       </c>
@@ -26133,7 +26133,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="315" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A315" s="1">
         <v>275</v>
       </c>
@@ -26210,7 +26210,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="316" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>275</v>
       </c>
@@ -26287,7 +26287,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="317" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>275</v>
       </c>
@@ -26364,7 +26364,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="318" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>275</v>
       </c>
@@ -26441,7 +26441,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="319" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>276</v>
       </c>
@@ -26506,7 +26506,7 @@
       <c r="X319" s="3"/>
       <c r="Y319" s="3"/>
     </row>
-    <row r="320" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
         <v>277</v>
       </c>
@@ -26571,7 +26571,7 @@
       <c r="X320" s="3"/>
       <c r="Y320" s="3"/>
     </row>
-    <row r="321" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A321" s="1">
         <v>278</v>
       </c>
@@ -26648,7 +26648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>278</v>
       </c>
@@ -26725,7 +26725,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="323" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>278</v>
       </c>
@@ -26802,7 +26802,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="324" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>278</v>
       </c>
@@ -26879,7 +26879,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="325" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>282</v>
       </c>
@@ -26944,7 +26944,7 @@
       <c r="X325" s="3"/>
       <c r="Y325" s="3"/>
     </row>
-    <row r="326" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>283</v>
       </c>
@@ -27009,7 +27009,7 @@
       <c r="X326" s="3"/>
       <c r="Y326" s="3"/>
     </row>
-    <row r="327" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>285</v>
       </c>
@@ -27074,7 +27074,7 @@
       <c r="X327" s="3"/>
       <c r="Y327" s="3"/>
     </row>
-    <row r="328" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A328" s="1">
         <v>286</v>
       </c>
@@ -27151,7 +27151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>286</v>
       </c>
@@ -27228,7 +27228,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="330" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>286</v>
       </c>
@@ -27305,7 +27305,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="331" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>286</v>
       </c>
@@ -27382,7 +27382,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="332" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>286</v>
       </c>
@@ -27459,7 +27459,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="333" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A333" s="1">
         <v>292</v>
       </c>
@@ -27536,7 +27536,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="334" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>292</v>
       </c>
@@ -27613,7 +27613,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="335" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>292</v>
       </c>
@@ -27690,7 +27690,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="336" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>292</v>
       </c>
@@ -27767,7 +27767,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="337" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A337" s="1">
         <v>294</v>
       </c>
@@ -27844,7 +27844,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="338" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>294</v>
       </c>
@@ -27921,7 +27921,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="339" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>294</v>
       </c>
@@ -27998,7 +27998,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="340" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>294</v>
       </c>
@@ -28075,7 +28075,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="341" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A341" s="1">
         <v>302</v>
       </c>
@@ -28152,7 +28152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>302</v>
       </c>
@@ -28229,7 +28229,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="343" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>302</v>
       </c>
@@ -28306,7 +28306,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="344" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>302</v>
       </c>
@@ -28383,7 +28383,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="345" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>302</v>
       </c>
@@ -28460,7 +28460,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="346" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A346" s="1">
         <v>303</v>
       </c>
@@ -28535,7 +28535,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="347" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>303</v>
       </c>
@@ -28612,7 +28612,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="348" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>303</v>
       </c>
@@ -28689,7 +28689,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="349" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>303</v>
       </c>
@@ -28766,7 +28766,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="350" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
         <v>304</v>
       </c>
@@ -28831,7 +28831,7 @@
       <c r="X350" s="3"/>
       <c r="Y350" s="3"/>
     </row>
-    <row r="351" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
         <v>323</v>
       </c>
@@ -28896,7 +28896,7 @@
       <c r="X351" s="3"/>
       <c r="Y351" s="3"/>
     </row>
-    <row r="352" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
         <v>324</v>
       </c>
@@ -28961,7 +28961,7 @@
       <c r="X352" s="3"/>
       <c r="Y352" s="3"/>
     </row>
-    <row r="353" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A353" s="1">
         <v>325</v>
       </c>
@@ -29026,7 +29026,7 @@
       <c r="X353" s="3"/>
       <c r="Y353" s="3"/>
     </row>
-    <row r="354" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
         <v>327</v>
       </c>
@@ -29091,7 +29091,7 @@
       <c r="X354" s="3"/>
       <c r="Y354" s="3"/>
     </row>
-    <row r="355" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
         <v>332</v>
       </c>
@@ -29156,7 +29156,7 @@
       <c r="X355" s="3"/>
       <c r="Y355" s="3"/>
     </row>
-    <row r="356" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
         <v>337</v>
       </c>
@@ -29221,7 +29221,7 @@
       <c r="X356" s="3"/>
       <c r="Y356" s="3"/>
     </row>
-    <row r="357" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
         <v>338</v>
       </c>
@@ -29286,7 +29286,7 @@
       <c r="X357" s="3"/>
       <c r="Y357" s="3"/>
     </row>
-    <row r="358" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
         <v>341</v>
       </c>
@@ -29351,7 +29351,7 @@
       <c r="X358" s="3"/>
       <c r="Y358" s="3"/>
     </row>
-    <row r="359" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
         <v>344</v>
       </c>
@@ -29416,7 +29416,7 @@
       <c r="X359" s="3"/>
       <c r="Y359" s="3"/>
     </row>
-    <row r="360" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A360" s="1">
         <v>356</v>
       </c>
@@ -29481,7 +29481,7 @@
       <c r="X360" s="3"/>
       <c r="Y360" s="3"/>
     </row>
-    <row r="361" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
         <v>357</v>
       </c>
@@ -29542,7 +29542,7 @@
       <c r="X361" s="3"/>
       <c r="Y361" s="3"/>
     </row>
-    <row r="362" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A362" s="1">
         <v>358</v>
       </c>
@@ -29607,7 +29607,7 @@
       <c r="X362" s="3"/>
       <c r="Y362" s="3"/>
     </row>
-    <row r="363" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
         <v>359</v>
       </c>
@@ -29668,7 +29668,7 @@
       <c r="X363" s="3"/>
       <c r="Y363" s="3"/>
     </row>
-    <row r="364" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A364" s="1">
         <v>362</v>
       </c>
@@ -29745,7 +29745,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="365" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>362</v>
       </c>
@@ -29822,7 +29822,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="366" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>362</v>
       </c>
@@ -29899,7 +29899,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="367" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A367" s="1">
         <v>363</v>
       </c>
@@ -29962,7 +29962,7 @@
       <c r="X367" s="3"/>
       <c r="Y367" s="3"/>
     </row>
-    <row r="368" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A368" s="1">
         <v>364</v>
       </c>
@@ -30027,7 +30027,7 @@
       <c r="X368" s="3"/>
       <c r="Y368" s="3"/>
     </row>
-    <row r="369" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A369" s="1">
         <v>369</v>
       </c>
@@ -30104,7 +30104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>369</v>
       </c>
@@ -30181,7 +30181,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="371" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>369</v>
       </c>
@@ -30258,7 +30258,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="372" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A372" s="1">
         <v>371</v>
       </c>
@@ -30323,7 +30323,7 @@
       <c r="X372" s="3"/>
       <c r="Y372" s="3"/>
     </row>
-    <row r="373" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A373" s="1">
         <v>375</v>
       </c>
@@ -30400,7 +30400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>375</v>
       </c>
@@ -30477,7 +30477,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="375" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>375</v>
       </c>
@@ -30554,7 +30554,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="376" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A376" s="1">
         <v>376</v>
       </c>
@@ -30619,7 +30619,7 @@
       <c r="X376" s="3"/>
       <c r="Y376" s="3"/>
     </row>
-    <row r="377" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A377" s="1">
         <v>379</v>
       </c>
@@ -30684,7 +30684,7 @@
       <c r="X377" s="3"/>
       <c r="Y377" s="3"/>
     </row>
-    <row r="378" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A378" s="1">
         <v>381</v>
       </c>
@@ -30749,7 +30749,7 @@
       <c r="X378" s="3"/>
       <c r="Y378" s="3"/>
     </row>
-    <row r="379" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A379" s="1">
         <v>382</v>
       </c>
@@ -30814,7 +30814,7 @@
       <c r="X379" s="3"/>
       <c r="Y379" s="3"/>
     </row>
-    <row r="380" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A380" s="1">
         <v>383</v>
       </c>
@@ -30879,7 +30879,7 @@
       <c r="X380" s="3"/>
       <c r="Y380" s="3"/>
     </row>
-    <row r="381" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A381" s="1">
         <v>384</v>
       </c>
@@ -31009,7 +31009,7 @@
       <c r="X382" s="3"/>
       <c r="Y382" s="3"/>
     </row>
-    <row r="383" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A383" s="1">
         <v>386</v>
       </c>
@@ -31086,7 +31086,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="384" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>386</v>
       </c>
@@ -31163,7 +31163,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="385" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>386</v>
       </c>
@@ -31240,7 +31240,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="386" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>386</v>
       </c>
@@ -31317,7 +31317,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="387" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A387" s="1">
         <v>389</v>
       </c>
@@ -31390,7 +31390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>389</v>
       </c>
@@ -31464,7 +31464,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="389" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>389</v>
       </c>
@@ -31538,7 +31538,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="390" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>389</v>
       </c>
@@ -31612,7 +31612,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="391" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>389</v>
       </c>
@@ -31686,7 +31686,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="392" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>389</v>
       </c>
@@ -31760,7 +31760,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="393" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>389</v>
       </c>
@@ -31834,7 +31834,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="394" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>389</v>
       </c>
@@ -31908,7 +31908,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="395" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>389</v>
       </c>
@@ -31982,7 +31982,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="396" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>389</v>
       </c>
@@ -32056,7 +32056,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="397" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>389</v>
       </c>
@@ -32130,7 +32130,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="398" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>389</v>
       </c>
@@ -32204,7 +32204,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="399" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>389</v>
       </c>
@@ -32278,7 +32278,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="400" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A400" s="1">
         <v>397</v>
       </c>
@@ -32343,7 +32343,7 @@
       <c r="X400" s="3"/>
       <c r="Y400" s="3"/>
     </row>
-    <row r="401" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A401" s="1">
         <v>398</v>
       </c>
@@ -32408,7 +32408,7 @@
       <c r="X401" s="3"/>
       <c r="Y401" s="3"/>
     </row>
-    <row r="402" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A402" s="1">
         <v>399</v>
       </c>
@@ -32473,7 +32473,7 @@
       <c r="X402" s="3"/>
       <c r="Y402" s="3"/>
     </row>
-    <row r="403" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A403" s="1">
         <v>400</v>
       </c>
@@ -32538,7 +32538,7 @@
       <c r="X403" s="3"/>
       <c r="Y403" s="3"/>
     </row>
-    <row r="404" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A404" s="1">
         <v>401</v>
       </c>
@@ -32603,7 +32603,7 @@
       <c r="X404" s="3"/>
       <c r="Y404" s="3"/>
     </row>
-    <row r="405" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A405" s="1">
         <v>403</v>
       </c>
@@ -32668,7 +32668,7 @@
       <c r="X405" s="3"/>
       <c r="Y405" s="3"/>
     </row>
-    <row r="406" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A406" s="1">
         <v>408</v>
       </c>
@@ -32745,7 +32745,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="407" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>408</v>
       </c>
@@ -32822,7 +32822,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="408" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>408</v>
       </c>
@@ -32899,7 +32899,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="409" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>408</v>
       </c>
@@ -32976,7 +32976,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="410" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A410" s="1">
         <v>422</v>
       </c>
@@ -33041,7 +33041,7 @@
       <c r="X410" s="3"/>
       <c r="Y410" s="3"/>
     </row>
-    <row r="411" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A411" s="1">
         <v>426</v>
       </c>
@@ -33100,7 +33100,7 @@
       <c r="X411" s="3"/>
       <c r="Y411" s="3"/>
     </row>
-    <row r="412" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A412" s="1">
         <v>427</v>
       </c>
@@ -33177,7 +33177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>427</v>
       </c>
@@ -33254,7 +33254,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="414" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>427</v>
       </c>
@@ -33331,7 +33331,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="415" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>427</v>
       </c>
@@ -33408,7 +33408,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="416" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>427</v>
       </c>
@@ -33485,7 +33485,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="417" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>427</v>
       </c>
@@ -33558,7 +33558,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="418" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>427</v>
       </c>
@@ -33635,7 +33635,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="419" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A419" s="1">
         <v>428</v>
       </c>
@@ -33712,7 +33712,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="420" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>428</v>
       </c>
@@ -33789,7 +33789,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="421" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>428</v>
       </c>
@@ -33866,7 +33866,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="422" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>428</v>
       </c>
@@ -33941,7 +33941,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="423" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>428</v>
       </c>
@@ -34018,7 +34018,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="424" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>428</v>
       </c>
@@ -34091,7 +34091,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="425" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>428</v>
       </c>
@@ -34166,7 +34166,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="426" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>428</v>
       </c>
@@ -34220,7 +34220,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="427" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A427" s="1">
         <v>429</v>
       </c>
@@ -34297,7 +34297,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="428" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>429</v>
       </c>
@@ -34374,7 +34374,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="429" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>429</v>
       </c>
@@ -34451,7 +34451,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="430" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>429</v>
       </c>
@@ -34528,7 +34528,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="431" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>429</v>
       </c>
@@ -34605,7 +34605,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="432" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>429</v>
       </c>
@@ -34682,7 +34682,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="433" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>429</v>
       </c>
@@ -34759,7 +34759,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="434" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A434" s="1">
         <v>430</v>
       </c>
@@ -34836,7 +34836,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="435" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>430</v>
       </c>
@@ -34913,7 +34913,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="436" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>430</v>
       </c>
@@ -34990,7 +34990,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="437" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>430</v>
       </c>
@@ -35067,7 +35067,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="438" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A438">
         <v>430</v>
       </c>
@@ -35144,7 +35144,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="439" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A439" s="1">
         <v>433</v>
       </c>
@@ -35221,7 +35221,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="440" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>433</v>
       </c>
@@ -35298,7 +35298,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="441" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>433</v>
       </c>
@@ -35375,7 +35375,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="442" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>433</v>
       </c>
@@ -35452,7 +35452,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="443" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>433</v>
       </c>
@@ -35525,7 +35525,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="444" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>433</v>
       </c>
@@ -35596,7 +35596,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="445" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>433</v>
       </c>
@@ -35671,7 +35671,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="446" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A446">
         <v>433</v>
       </c>
@@ -35729,7 +35729,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="447" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A447" s="1">
         <v>435</v>
       </c>
@@ -35804,7 +35804,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="448" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>435</v>
       </c>
@@ -35881,7 +35881,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="449" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>435</v>
       </c>
@@ -35958,7 +35958,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="450" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>435</v>
       </c>
@@ -36035,7 +36035,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="451" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>435</v>
       </c>
@@ -36112,7 +36112,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="452" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>435</v>
       </c>
@@ -36189,7 +36189,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="453" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A453">
         <v>435</v>
       </c>
@@ -36266,7 +36266,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="454" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A454" s="1">
         <v>439</v>
       </c>
@@ -36343,7 +36343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>439</v>
       </c>
@@ -36420,7 +36420,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="456" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>439</v>
       </c>
@@ -36497,7 +36497,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="457" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A457" s="1">
         <v>440</v>
       </c>
@@ -36574,7 +36574,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="458" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>440</v>
       </c>
@@ -36651,7 +36651,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="459" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A459">
         <v>440</v>
       </c>
@@ -36728,7 +36728,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="460" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A460" s="1">
         <v>444</v>
       </c>
@@ -36787,7 +36787,7 @@
       <c r="X460" s="3"/>
       <c r="Y460" s="3"/>
     </row>
-    <row r="461" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A461" s="1">
         <v>445</v>
       </c>
@@ -36848,7 +36848,7 @@
       <c r="X461" s="3"/>
       <c r="Y461" s="3"/>
     </row>
-    <row r="462" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A462" s="1">
         <v>447</v>
       </c>
@@ -36909,7 +36909,7 @@
       <c r="X462" s="3"/>
       <c r="Y462" s="3"/>
     </row>
-    <row r="463" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A463" s="1">
         <v>448</v>
       </c>
@@ -36970,7 +36970,7 @@
       <c r="X463" s="3"/>
       <c r="Y463" s="3"/>
     </row>
-    <row r="464" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A464" s="1">
         <v>451</v>
       </c>
@@ -37031,7 +37031,7 @@
       <c r="X464" s="3"/>
       <c r="Y464" s="3"/>
     </row>
-    <row r="465" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A465" s="1">
         <v>452</v>
       </c>
@@ -37088,7 +37088,7 @@
       <c r="X465" s="3"/>
       <c r="Y465" s="3"/>
     </row>
-    <row r="466" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A466" s="1">
         <v>466</v>
       </c>
@@ -37149,7 +37149,7 @@
       <c r="X466" s="3"/>
       <c r="Y466" s="3"/>
     </row>
-    <row r="467" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A467" s="1">
         <v>467</v>
       </c>
@@ -37210,7 +37210,7 @@
       <c r="X467" s="3"/>
       <c r="Y467" s="3"/>
     </row>
-    <row r="468" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A468" s="1">
         <v>468</v>
       </c>
@@ -37271,7 +37271,7 @@
       <c r="X468" s="3"/>
       <c r="Y468" s="3"/>
     </row>
-    <row r="469" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A469" s="1">
         <v>473</v>
       </c>
@@ -37348,7 +37348,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="470" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>473</v>
       </c>
@@ -37425,7 +37425,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="471" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>473</v>
       </c>
@@ -37502,7 +37502,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="472" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A472">
         <v>473</v>
       </c>
@@ -37579,7 +37579,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="473" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A473" s="1">
         <v>474</v>
       </c>
@@ -37652,7 +37652,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="474" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>474</v>
       </c>
@@ -37726,7 +37726,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="475" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>474</v>
       </c>
@@ -37800,7 +37800,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="476" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>474</v>
       </c>
@@ -37874,7 +37874,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="477" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>474</v>
       </c>
@@ -37948,7 +37948,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="478" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A478">
         <v>474</v>
       </c>
@@ -38022,7 +38022,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="479" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>474</v>
       </c>
@@ -38096,7 +38096,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="480" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>474</v>
       </c>
@@ -38170,7 +38170,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="481" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>474</v>
       </c>
@@ -38244,7 +38244,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="482" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>474</v>
       </c>
@@ -38318,7 +38318,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="483" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>474</v>
       </c>
@@ -38392,7 +38392,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="484" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>474</v>
       </c>
@@ -38466,7 +38466,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="485" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A485">
         <v>474</v>
       </c>
@@ -38540,7 +38540,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="486" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A486" s="1">
         <v>475</v>
       </c>
@@ -38601,7 +38601,7 @@
       <c r="X486" s="3"/>
       <c r="Y486" s="3"/>
     </row>
-    <row r="487" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A487" s="1">
         <v>476</v>
       </c>
@@ -38678,7 +38678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="488" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>476</v>
       </c>
@@ -38755,7 +38755,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="489" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>476</v>
       </c>
@@ -38832,7 +38832,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="490" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A490">
         <v>476</v>
       </c>
@@ -38909,7 +38909,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="491" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A491" s="1">
         <v>477</v>
       </c>
@@ -38980,7 +38980,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="492" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>477</v>
       </c>
@@ -39054,7 +39054,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="493" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>477</v>
       </c>
@@ -39128,7 +39128,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="494" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>477</v>
       </c>
@@ -39202,7 +39202,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="495" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A495">
         <v>477</v>
       </c>
@@ -39276,7 +39276,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="496" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A496">
         <v>477</v>
       </c>
@@ -39350,7 +39350,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="497" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A497">
         <v>477</v>
       </c>
@@ -39424,7 +39424,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="498" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A498">
         <v>477</v>
       </c>
@@ -39498,7 +39498,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="499" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A499">
         <v>477</v>
       </c>
@@ -39572,7 +39572,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="500" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A500">
         <v>477</v>
       </c>
@@ -39646,7 +39646,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="501" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A501">
         <v>477</v>
       </c>
@@ -39720,7 +39720,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="502" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A502">
         <v>477</v>
       </c>
@@ -39794,7 +39794,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="503" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A503">
         <v>477</v>
       </c>
@@ -39868,7 +39868,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="504" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A504" s="1">
         <v>478</v>
       </c>
@@ -39941,7 +39941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="505" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A505">
         <v>478</v>
       </c>
@@ -40015,7 +40015,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="506" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A506">
         <v>478</v>
       </c>
@@ -40089,7 +40089,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="507" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A507">
         <v>478</v>
       </c>
@@ -40163,7 +40163,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="508" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A508">
         <v>478</v>
       </c>
@@ -40237,7 +40237,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="509" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A509">
         <v>478</v>
       </c>
@@ -40311,7 +40311,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="510" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A510">
         <v>478</v>
       </c>
@@ -40385,7 +40385,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="511" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A511">
         <v>478</v>
       </c>
@@ -40459,7 +40459,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="512" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A512">
         <v>478</v>
       </c>
@@ -40533,7 +40533,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="513" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A513">
         <v>478</v>
       </c>
@@ -40607,7 +40607,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="514" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A514">
         <v>478</v>
       </c>
@@ -40681,7 +40681,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="515" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A515">
         <v>478</v>
       </c>
@@ -40755,7 +40755,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="516" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A516">
         <v>478</v>
       </c>
@@ -40829,7 +40829,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="517" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A517" s="1">
         <v>479</v>
       </c>
@@ -40902,7 +40902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="518" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A518">
         <v>479</v>
       </c>
@@ -40979,7 +40979,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="519" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A519">
         <v>479</v>
       </c>
@@ -41056,7 +41056,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="520" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A520">
         <v>479</v>
       </c>
@@ -41133,7 +41133,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="521" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A521">
         <v>479</v>
       </c>
@@ -41210,7 +41210,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="522" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A522">
         <v>479</v>
       </c>
@@ -41287,7 +41287,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="523" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A523">
         <v>479</v>
       </c>
@@ -41364,7 +41364,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="524" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A524">
         <v>479</v>
       </c>
@@ -41441,7 +41441,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="525" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A525">
         <v>479</v>
       </c>
@@ -41518,7 +41518,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="526" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A526">
         <v>479</v>
       </c>
@@ -41595,7 +41595,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="527" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A527">
         <v>479</v>
       </c>
@@ -41672,7 +41672,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="528" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A528">
         <v>479</v>
       </c>
@@ -41749,7 +41749,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="529" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A529">
         <v>479</v>
       </c>
@@ -41826,7 +41826,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="530" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A530" s="1">
         <v>480</v>
       </c>
@@ -41899,7 +41899,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="531" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A531">
         <v>480</v>
       </c>
@@ -41976,7 +41976,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="532" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A532">
         <v>480</v>
       </c>
@@ -42053,7 +42053,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="533" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A533">
         <v>480</v>
       </c>
@@ -42130,7 +42130,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="534" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A534">
         <v>480</v>
       </c>
@@ -42207,7 +42207,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="535" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A535">
         <v>480</v>
       </c>
@@ -42284,7 +42284,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="536" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A536">
         <v>480</v>
       </c>
@@ -42361,7 +42361,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="537" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A537">
         <v>480</v>
       </c>
@@ -42438,7 +42438,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="538" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A538">
         <v>480</v>
       </c>
@@ -42515,7 +42515,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="539" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A539">
         <v>480</v>
       </c>
@@ -42592,7 +42592,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="540" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A540">
         <v>480</v>
       </c>
@@ -42669,7 +42669,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="541" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A541">
         <v>480</v>
       </c>
@@ -42746,7 +42746,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="542" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A542">
         <v>480</v>
       </c>
@@ -42823,7 +42823,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="543" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A543" s="1">
         <v>481</v>
       </c>
@@ -42884,7 +42884,7 @@
       <c r="X543" s="3"/>
       <c r="Y543" s="3"/>
     </row>
-    <row r="544" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A544">
         <v>481</v>
       </c>
@@ -42954,7 +42954,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="545" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A545" s="1">
         <v>486</v>
       </c>
@@ -43013,7 +43013,7 @@
       <c r="X545" s="3"/>
       <c r="Y545" s="3"/>
     </row>
-    <row r="546" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A546" s="1">
         <v>506</v>
       </c>
@@ -43072,7 +43072,7 @@
       <c r="X546" s="3"/>
       <c r="Y546" s="3"/>
     </row>
-    <row r="547" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A547" s="1">
         <v>507</v>
       </c>
@@ -43131,7 +43131,7 @@
       <c r="X547" s="3"/>
       <c r="Y547" s="3"/>
     </row>
-    <row r="548" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A548" s="1">
         <v>514</v>
       </c>
@@ -43188,7 +43188,7 @@
       <c r="X548" s="3"/>
       <c r="Y548" s="3"/>
     </row>
-    <row r="549" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A549" s="1">
         <v>515</v>
       </c>
@@ -43243,7 +43243,7 @@
       <c r="X549" s="3"/>
       <c r="Y549" s="3"/>
     </row>
-    <row r="550" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A550" s="1">
         <v>516</v>
       </c>
@@ -43298,7 +43298,7 @@
       <c r="X550" s="3"/>
       <c r="Y550" s="3"/>
     </row>
-    <row r="551" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A551" s="1">
         <v>519</v>
       </c>
@@ -43375,7 +43375,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="552" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A552">
         <v>519</v>
       </c>
@@ -43452,7 +43452,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="553" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A553">
         <v>519</v>
       </c>
@@ -43529,7 +43529,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="554" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A554" s="1">
         <v>523</v>
       </c>
@@ -43606,7 +43606,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="555" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A555">
         <v>523</v>
       </c>
@@ -43683,7 +43683,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="556" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A556">
         <v>523</v>
       </c>
@@ -43760,7 +43760,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="557" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A557">
         <v>523</v>
       </c>
@@ -43837,7 +43837,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="558" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A558" s="1">
         <v>524</v>
       </c>
@@ -43914,7 +43914,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="559" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A559">
         <v>524</v>
       </c>
@@ -43991,7 +43991,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="560" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A560">
         <v>524</v>
       </c>
@@ -44068,7 +44068,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="561" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A561">
         <v>524</v>
       </c>
@@ -44145,7 +44145,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="562" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A562">
         <v>524</v>
       </c>
@@ -44222,7 +44222,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="563" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A563">
         <v>524</v>
       </c>
@@ -44299,7 +44299,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="564" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A564">
         <v>524</v>
       </c>
@@ -44376,7 +44376,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="565" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A565" s="1">
         <v>530</v>
       </c>
@@ -44431,7 +44431,7 @@
       <c r="X565" s="3"/>
       <c r="Y565" s="3"/>
     </row>
-    <row r="566" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A566" s="1">
         <v>531</v>
       </c>
@@ -44486,7 +44486,7 @@
       <c r="X566" s="3"/>
       <c r="Y566" s="3"/>
     </row>
-    <row r="567" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A567" s="1">
         <v>532</v>
       </c>
@@ -44555,7 +44555,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="568" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A568">
         <v>532</v>
       </c>
@@ -44632,7 +44632,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="569" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A569">
         <v>532</v>
       </c>
@@ -44709,7 +44709,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="570" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A570">
         <v>532</v>
       </c>
@@ -44786,7 +44786,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="571" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A571">
         <v>532</v>
       </c>
@@ -44863,7 +44863,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="572" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A572" s="1">
         <v>533</v>
       </c>
@@ -44940,7 +44940,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="573" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A573">
         <v>533</v>
       </c>
@@ -45017,7 +45017,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="574" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A574">
         <v>533</v>
       </c>
@@ -45094,7 +45094,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="575" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A575" s="1">
         <v>534</v>
       </c>
@@ -45171,7 +45171,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="576" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A576">
         <v>534</v>
       </c>
@@ -45248,7 +45248,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="577" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A577">
         <v>534</v>
       </c>
@@ -45325,7 +45325,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="578" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A578" s="1">
         <v>535</v>
       </c>
@@ -45402,7 +45402,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="579" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A579">
         <v>535</v>
       </c>
@@ -45479,7 +45479,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="580" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A580">
         <v>535</v>
       </c>
@@ -45556,7 +45556,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="581" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A581" s="1">
         <v>536</v>
       </c>
@@ -45633,7 +45633,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="582" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A582">
         <v>536</v>
       </c>
@@ -45710,7 +45710,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="583" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A583">
         <v>536</v>
       </c>
@@ -45787,7 +45787,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="584" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A584" s="1">
         <v>537</v>
       </c>
@@ -45844,7 +45844,7 @@
       <c r="X584" s="3"/>
       <c r="Y584" s="3"/>
     </row>
-    <row r="585" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A585" s="1">
         <v>538</v>
       </c>
@@ -45899,7 +45899,7 @@
       <c r="X585" s="3"/>
       <c r="Y585" s="3"/>
     </row>
-    <row r="586" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A586" s="1">
         <v>539</v>
       </c>
@@ -45954,7 +45954,7 @@
       <c r="X586" s="3"/>
       <c r="Y586" s="3"/>
     </row>
-    <row r="587" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A587" s="1">
         <v>540</v>
       </c>
@@ -46011,7 +46011,7 @@
       <c r="X587" s="3"/>
       <c r="Y587" s="3"/>
     </row>
-    <row r="588" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A588" s="1">
         <v>543</v>
       </c>
@@ -46086,7 +46086,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="589" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A589">
         <v>543</v>
       </c>
@@ -46163,7 +46163,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="590" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A590">
         <v>543</v>
       </c>
@@ -46240,7 +46240,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="591" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A591" s="1">
         <v>544</v>
       </c>
@@ -46315,7 +46315,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="592" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A592">
         <v>544</v>
       </c>
@@ -46392,7 +46392,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="593" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A593">
         <v>544</v>
       </c>
@@ -46469,7 +46469,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="594" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A594">
         <v>544</v>
       </c>
@@ -46546,7 +46546,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="595" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A595">
         <v>544</v>
       </c>
@@ -46623,7 +46623,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="596" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A596" s="1">
         <v>550</v>
       </c>
@@ -46680,7 +46680,7 @@
       <c r="X596" s="3"/>
       <c r="Y596" s="3"/>
     </row>
-    <row r="597" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A597" s="1">
         <v>551</v>
       </c>
@@ -46737,7 +46737,7 @@
       <c r="X597" s="3"/>
       <c r="Y597" s="3"/>
     </row>
-    <row r="598" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A598" s="1">
         <v>554</v>
       </c>
@@ -46792,7 +46792,7 @@
       <c r="X598" s="3"/>
       <c r="Y598" s="3"/>
     </row>
-    <row r="599" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A599" s="1">
         <v>555</v>
       </c>
@@ -46847,7 +46847,7 @@
       <c r="X599" s="3"/>
       <c r="Y599" s="3"/>
     </row>
-    <row r="600" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A600" s="1">
         <v>69</v>
       </c>
@@ -46924,7 +46924,7 @@
         <v>90.541781450871994</v>
       </c>
     </row>
-    <row r="601" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A601" s="1">
         <v>111</v>
       </c>
@@ -47001,7 +47001,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="602" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A602" s="1">
         <v>197</v>
       </c>
@@ -47078,7 +47078,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="603" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A603" s="1">
         <v>213</v>
       </c>
@@ -47155,7 +47155,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="604" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A604">
         <v>213</v>
       </c>
@@ -47232,7 +47232,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="605" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A605">
         <v>213</v>
       </c>
@@ -47309,7 +47309,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="606" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A606">
         <v>213</v>
       </c>
@@ -47386,7 +47386,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="607" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A607">
         <v>213</v>
       </c>
@@ -47463,7 +47463,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="608" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A608">
         <v>213</v>
       </c>
@@ -47540,7 +47540,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="609" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A609">
         <v>213</v>
       </c>
@@ -47617,7 +47617,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="610" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A610">
         <v>213</v>
       </c>
@@ -47694,7 +47694,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="611" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A611">
         <v>213</v>
       </c>
@@ -47771,7 +47771,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="612" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A612" s="1">
         <v>233</v>
       </c>
@@ -47846,7 +47846,7 @@
         <v>64.367816091954026</v>
       </c>
     </row>
-    <row r="613" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A613" s="1">
         <v>234</v>
       </c>
@@ -47921,7 +47921,7 @@
         <v>3692.25</v>
       </c>
     </row>
-    <row r="614" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A614" s="1">
         <v>238</v>
       </c>
@@ -47994,7 +47994,7 @@
         <v>94.444444444444443</v>
       </c>
     </row>
-    <row r="615" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A615">
         <v>238</v>
       </c>
@@ -48071,7 +48071,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="616" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A616">
         <v>238</v>
       </c>
@@ -48148,7 +48148,7 @@
         <v>83.33</v>
       </c>
     </row>
-    <row r="617" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A617">
         <v>238</v>
       </c>
@@ -48225,7 +48225,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="618" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A618">
         <v>238</v>
       </c>
@@ -48302,7 +48302,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="619" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A619">
         <v>238</v>
       </c>
@@ -48379,7 +48379,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="620" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A620">
         <v>238</v>
       </c>
@@ -48456,7 +48456,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="621" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A621">
         <v>238</v>
       </c>
@@ -48533,7 +48533,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="622" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A622">
         <v>238</v>
       </c>
@@ -48610,7 +48610,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="623" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A623" s="1">
         <v>240</v>
       </c>
@@ -48685,7 +48685,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="624" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A624" s="1">
         <v>251</v>
       </c>
@@ -48760,7 +48760,7 @@
       </c>
       <c r="Y624" s="3"/>
     </row>
-    <row r="625" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A625" s="1">
         <v>254</v>
       </c>
@@ -48816,7 +48816,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="626" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A626" s="1">
         <v>263</v>
       </c>
@@ -48893,7 +48893,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="627" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A627" s="1">
         <v>265</v>
       </c>
@@ -48970,7 +48970,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="628" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A628" s="1">
         <v>266</v>
       </c>
@@ -49047,7 +49047,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="629" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A629" s="1">
         <v>300</v>
       </c>
@@ -49124,7 +49124,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="630" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A630" s="1">
         <v>301</v>
       </c>
@@ -49201,7 +49201,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="631" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A631" s="1">
         <v>306</v>
       </c>
@@ -49276,7 +49276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="632" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A632">
         <v>306</v>
       </c>
@@ -49353,7 +49353,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="633" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A633">
         <v>306</v>
       </c>
@@ -49430,7 +49430,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="634" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A634">
         <v>306</v>
       </c>
@@ -49507,7 +49507,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="635" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A635">
         <v>306</v>
       </c>
@@ -49584,7 +49584,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="636" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A636">
         <v>306</v>
       </c>
@@ -49661,7 +49661,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="637" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A637">
         <v>306</v>
       </c>
@@ -49738,7 +49738,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="638" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A638" s="1">
         <v>347</v>
       </c>
@@ -49815,7 +49815,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="639" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A639" s="1">
         <v>348</v>
       </c>
@@ -49892,7 +49892,7 @@
         <v>99.936143039591002</v>
       </c>
     </row>
-    <row r="640" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A640" s="1">
         <v>351</v>
       </c>
@@ -49967,7 +49967,7 @@
         <v>11.41868512110727</v>
       </c>
     </row>
-    <row r="641" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A641" s="1">
         <v>352</v>
       </c>
@@ -50042,7 +50042,7 @@
         <v>1.0385968556480199E-2</v>
       </c>
     </row>
-    <row r="642" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A642" s="1">
         <v>368</v>
       </c>
@@ -50115,7 +50115,7 @@
       <c r="X642" s="3"/>
       <c r="Y642" s="3"/>
     </row>
-    <row r="643" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A643" s="1">
         <v>372</v>
       </c>
@@ -50188,7 +50188,7 @@
       <c r="X643" s="3"/>
       <c r="Y643" s="3"/>
     </row>
-    <row r="644" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A644" s="1">
         <v>373</v>
       </c>
@@ -50265,7 +50265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="645" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A645">
         <v>373</v>
       </c>
@@ -50342,7 +50342,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="646" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A646">
         <v>373</v>
       </c>
@@ -50419,7 +50419,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="647" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A647">
         <v>373</v>
       </c>
@@ -50496,7 +50496,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="648" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A648">
         <v>373</v>
       </c>
@@ -50573,7 +50573,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="649" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A649">
         <v>373</v>
       </c>
@@ -50650,7 +50650,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="650" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A650">
         <v>373</v>
       </c>
@@ -50727,7 +50727,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="651" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A651" s="1">
         <v>390</v>
       </c>
@@ -50804,7 +50804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="652" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A652">
         <v>390</v>
       </c>
@@ -50881,7 +50881,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="653" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A653">
         <v>390</v>
       </c>
@@ -50958,7 +50958,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="654" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A654">
         <v>390</v>
       </c>
@@ -51035,7 +51035,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="655" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A655">
         <v>390</v>
       </c>
@@ -51112,7 +51112,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="656" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A656">
         <v>390</v>
       </c>
@@ -51189,7 +51189,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="657" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A657">
         <v>390</v>
       </c>
@@ -51266,7 +51266,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="658" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A658">
         <v>390</v>
       </c>
@@ -51343,7 +51343,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="659" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A659">
         <v>390</v>
       </c>
@@ -51420,7 +51420,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="660" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A660">
         <v>390</v>
       </c>
@@ -51497,7 +51497,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="661" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A661">
         <v>390</v>
       </c>
@@ -51574,7 +51574,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="662" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A662">
         <v>390</v>
       </c>
@@ -51651,7 +51651,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="663" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A663">
         <v>390</v>
       </c>
@@ -51728,7 +51728,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="664" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A664" s="1">
         <v>394</v>
       </c>
@@ -51805,7 +51805,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="665" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A665" s="1">
         <v>395</v>
       </c>
@@ -51880,7 +51880,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="666" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A666" s="1">
         <v>409</v>
       </c>
@@ -51951,7 +51951,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="667" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A667">
         <v>409</v>
       </c>
@@ -52028,7 +52028,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="668" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A668">
         <v>409</v>
       </c>
@@ -52105,7 +52105,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="669" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A669" s="1">
         <v>414</v>
       </c>
@@ -52182,7 +52182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="670" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A670">
         <v>414</v>
       </c>
@@ -52259,7 +52259,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="671" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A671">
         <v>414</v>
       </c>
@@ -52336,7 +52336,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="672" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A672">
         <v>414</v>
       </c>
@@ -52413,7 +52413,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="673" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A673">
         <v>414</v>
       </c>
@@ -52490,7 +52490,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="674" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A674">
         <v>414</v>
       </c>
@@ -52567,7 +52567,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="675" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A675">
         <v>414</v>
       </c>
@@ -52644,7 +52644,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="676" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A676">
         <v>414</v>
       </c>
@@ -52721,7 +52721,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="677" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A677">
         <v>414</v>
       </c>
@@ -52798,7 +52798,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="678" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A678">
         <v>414</v>
       </c>
@@ -52875,7 +52875,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="679" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A679" s="1">
         <v>415</v>
       </c>
@@ -52952,7 +52952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="680" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A680">
         <v>415</v>
       </c>
@@ -53029,7 +53029,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="681" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A681">
         <v>415</v>
       </c>
@@ -53106,7 +53106,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="682" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A682">
         <v>415</v>
       </c>
@@ -53183,7 +53183,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="683" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A683">
         <v>415</v>
       </c>
@@ -53260,7 +53260,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="684" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A684">
         <v>415</v>
       </c>
@@ -53337,7 +53337,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="685" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A685">
         <v>415</v>
       </c>
@@ -53414,7 +53414,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="686" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A686">
         <v>415</v>
       </c>
@@ -53491,7 +53491,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="687" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A687">
         <v>415</v>
       </c>
@@ -53568,7 +53568,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="688" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A688">
         <v>415</v>
       </c>
@@ -53645,7 +53645,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="689" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A689">
         <v>415</v>
       </c>
@@ -53722,7 +53722,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="690" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A690">
         <v>415</v>
       </c>
@@ -53799,7 +53799,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="691" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A691">
         <v>415</v>
       </c>
@@ -53876,7 +53876,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="692" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A692">
         <v>415</v>
       </c>
@@ -53953,7 +53953,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="693" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A693">
         <v>415</v>
       </c>
@@ -54030,7 +54030,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="694" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A694" s="1">
         <v>416</v>
       </c>
@@ -54107,7 +54107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="695" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A695">
         <v>416</v>
       </c>
@@ -54184,7 +54184,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="696" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A696">
         <v>416</v>
       </c>
@@ -54261,7 +54261,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="697" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A697">
         <v>416</v>
       </c>
@@ -54338,7 +54338,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="698" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A698">
         <v>416</v>
       </c>
@@ -54415,7 +54415,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="699" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A699">
         <v>416</v>
       </c>
@@ -54492,7 +54492,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="700" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A700">
         <v>416</v>
       </c>
@@ -54569,7 +54569,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="701" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A701" s="1">
         <v>417</v>
       </c>
@@ -54646,7 +54646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="702" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A702">
         <v>417</v>
       </c>
@@ -54723,7 +54723,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="703" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A703">
         <v>417</v>
       </c>
@@ -54800,7 +54800,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="704" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A704">
         <v>417</v>
       </c>
@@ -54877,7 +54877,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="705" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A705">
         <v>417</v>
       </c>
@@ -54954,7 +54954,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="706" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A706">
         <v>417</v>
       </c>
@@ -55031,7 +55031,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="707" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A707">
         <v>417</v>
       </c>
@@ -55108,7 +55108,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="708" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A708" s="1">
         <v>418</v>
       </c>
@@ -55185,7 +55185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="709" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A709">
         <v>418</v>
       </c>
@@ -55262,7 +55262,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="710" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A710">
         <v>418</v>
       </c>
@@ -55339,7 +55339,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="711" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A711">
         <v>418</v>
       </c>
@@ -55416,7 +55416,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="712" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A712">
         <v>418</v>
       </c>
@@ -55491,7 +55491,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="713" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A713">
         <v>418</v>
       </c>
@@ -55568,7 +55568,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="714" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A714">
         <v>418</v>
       </c>
@@ -55645,7 +55645,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="715" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A715">
         <v>418</v>
       </c>
@@ -55722,7 +55722,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="716" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A716">
         <v>418</v>
       </c>
@@ -55799,7 +55799,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="717" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A717">
         <v>418</v>
       </c>
@@ -55876,7 +55876,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="718" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A718" s="1">
         <v>420</v>
       </c>
@@ -55953,7 +55953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="719" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A719">
         <v>420</v>
       </c>
@@ -56030,7 +56030,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="720" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A720">
         <v>420</v>
       </c>
@@ -56107,7 +56107,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="721" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A721">
         <v>420</v>
       </c>
@@ -56184,7 +56184,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="722" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A722">
         <v>420</v>
       </c>
@@ -56261,7 +56261,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="723" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A723">
         <v>420</v>
       </c>
@@ -56338,7 +56338,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="724" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A724">
         <v>420</v>
       </c>
@@ -56415,7 +56415,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="725" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A725" s="1">
         <v>431</v>
       </c>
@@ -56488,7 +56488,7 @@
       <c r="X725" s="3"/>
       <c r="Y725" s="3"/>
     </row>
-    <row r="726" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A726" s="1">
         <v>432</v>
       </c>
@@ -56565,7 +56565,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="727" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A727">
         <v>432</v>
       </c>
@@ -56642,7 +56642,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="728" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A728">
         <v>432</v>
       </c>
@@ -56719,7 +56719,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="729" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A729">
         <v>432</v>
       </c>
@@ -56796,7 +56796,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="730" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A730">
         <v>432</v>
       </c>
@@ -56873,7 +56873,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="731" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A731">
         <v>432</v>
       </c>
@@ -56950,7 +56950,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="732" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A732">
         <v>432</v>
       </c>
@@ -57027,7 +57027,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="733" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A733">
         <v>432</v>
       </c>
@@ -57104,7 +57104,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="734" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A734">
         <v>432</v>
       </c>
@@ -57181,7 +57181,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="735" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A735">
         <v>432</v>
       </c>
@@ -57258,7 +57258,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="736" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A736" s="1">
         <v>453</v>
       </c>
@@ -57327,7 +57327,7 @@
       <c r="X736" s="3"/>
       <c r="Y736" s="3"/>
     </row>
-    <row r="737" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A737" s="1">
         <v>455</v>
       </c>
@@ -57392,7 +57392,7 @@
       <c r="X737" s="3"/>
       <c r="Y737" s="3"/>
     </row>
-    <row r="738" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A738" s="1">
         <v>456</v>
       </c>
@@ -57463,7 +57463,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="739" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A739">
         <v>456</v>
       </c>
@@ -57540,7 +57540,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="740" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A740">
         <v>456</v>
       </c>
@@ -57617,7 +57617,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="741" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A741">
         <v>456</v>
       </c>
@@ -57694,7 +57694,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="742" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A742" s="1">
         <v>457</v>
       </c>
@@ -57765,7 +57765,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="743" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A743">
         <v>457</v>
       </c>
@@ -57842,7 +57842,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="744" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A744">
         <v>457</v>
       </c>
@@ -57919,7 +57919,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="745" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A745">
         <v>457</v>
       </c>
@@ -57996,7 +57996,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="746" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A746" s="1">
         <v>469</v>
       </c>
@@ -58071,7 +58071,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="747" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A747">
         <v>469</v>
       </c>
@@ -58148,7 +58148,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="748" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A748">
         <v>469</v>
       </c>
@@ -58225,7 +58225,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="749" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A749">
         <v>469</v>
       </c>
@@ -58302,7 +58302,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="750" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A750">
         <v>469</v>
       </c>
@@ -58379,7 +58379,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="751" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A751">
         <v>469</v>
       </c>
@@ -58456,7 +58456,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="752" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A752">
         <v>469</v>
       </c>
@@ -58533,7 +58533,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="753" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A753">
         <v>469</v>
       </c>
@@ -58610,7 +58610,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="754" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A754">
         <v>469</v>
       </c>
@@ -58687,7 +58687,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="755" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A755">
         <v>469</v>
       </c>
@@ -58764,7 +58764,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="756" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A756">
         <v>469</v>
       </c>
@@ -58841,7 +58841,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="757" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A757" s="1">
         <v>470</v>
       </c>
@@ -58918,7 +58918,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="758" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A758">
         <v>470</v>
       </c>
@@ -58993,7 +58993,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="759" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A759">
         <v>470</v>
       </c>
@@ -59070,7 +59070,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="760" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A760">
         <v>470</v>
       </c>
@@ -59147,7 +59147,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="761" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A761">
         <v>470</v>
       </c>
@@ -59224,7 +59224,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="762" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A762">
         <v>470</v>
       </c>
@@ -59301,7 +59301,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="763" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A763" s="1">
         <v>471</v>
       </c>
@@ -59378,7 +59378,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="764" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A764">
         <v>471</v>
       </c>
@@ -59455,7 +59455,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="765" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A765">
         <v>471</v>
       </c>
@@ -59532,7 +59532,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="766" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A766">
         <v>471</v>
       </c>
@@ -59609,7 +59609,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="767" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A767">
         <v>471</v>
       </c>
@@ -59686,7 +59686,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="768" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A768">
         <v>471</v>
       </c>
@@ -59763,7 +59763,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="769" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A769">
         <v>471</v>
       </c>
@@ -59840,7 +59840,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="770" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A770">
         <v>471</v>
       </c>
@@ -59917,7 +59917,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="771" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A771" s="1">
         <v>484</v>
       </c>
@@ -59984,7 +59984,7 @@
       <c r="X771" s="3"/>
       <c r="Y771" s="3"/>
     </row>
-    <row r="772" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A772" s="1">
         <v>510</v>
       </c>
@@ -60059,7 +60059,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="773" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A773">
         <v>510</v>
       </c>
@@ -60130,7 +60130,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="774" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A774" s="1">
         <v>511</v>
       </c>
@@ -60205,7 +60205,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="775" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A775">
         <v>511</v>
       </c>
@@ -60282,7 +60282,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="776" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A776">
         <v>511</v>
       </c>
@@ -60359,7 +60359,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="777" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A777">
         <v>511</v>
       </c>
@@ -60436,7 +60436,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="778" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A778">
         <v>511</v>
       </c>
@@ -60513,7 +60513,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="779" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A779">
         <v>511</v>
       </c>
@@ -60590,7 +60590,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="780" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A780">
         <v>511</v>
       </c>
@@ -60667,7 +60667,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="781" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A781">
         <v>511</v>
       </c>
@@ -60744,7 +60744,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="782" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A782" s="1">
         <v>513</v>
       </c>
@@ -60805,7 +60805,7 @@
       <c r="X782" s="3"/>
       <c r="Y782" s="3"/>
     </row>
-    <row r="783" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A783" s="1">
         <v>518</v>
       </c>
@@ -60859,7 +60859,7 @@
       </c>
       <c r="R783" s="3"/>
     </row>
-    <row r="784" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A784" s="1">
         <v>526</v>
       </c>
@@ -60916,7 +60916,7 @@
       <c r="X784" s="3"/>
       <c r="Y784" s="3"/>
     </row>
-    <row r="785" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A785" s="1">
         <v>529</v>
       </c>
@@ -60991,7 +60991,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="786" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A786">
         <v>529</v>
       </c>
@@ -61068,7 +61068,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="787" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A787">
         <v>529</v>
       </c>
@@ -61147,15 +61147,1513 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter ref="A1:Y787" xr:uid="{69DEF77A-E506-4471-8935-B3BC88D629C9}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="385"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3954112-B764-41D3-B005-6FD07A474463}">
+  <dimension ref="A1:A299"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111" s="1">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118" s="1">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119" s="1">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120" s="1">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121" s="1">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122" s="1">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123" s="1">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A124" s="1">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125" s="1">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A126" s="1">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127" s="1">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128" s="1">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129" s="1">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" s="1">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A132" s="1">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A133" s="1">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A134" s="1">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A135" s="1">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A136" s="1">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A137" s="1">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A138" s="1">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A139" s="1">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A140" s="1">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A141" s="1">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A142" s="1">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A143" s="1">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A144" s="1">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A145" s="1">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A146" s="1">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A147" s="1">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A148" s="1">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A149" s="1">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A150" s="1">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A151" s="1">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A152" s="1">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A153" s="1">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A154" s="1">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A155" s="1">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A156" s="1">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A157" s="1">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A158" s="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A159" s="1">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A160" s="1">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A161" s="1">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A162" s="1">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A163" s="1">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A164" s="1">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A165" s="1">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A166" s="1">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A167" s="1">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A168" s="1">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A169" s="1">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A170" s="1">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A171" s="1">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A172" s="1">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A173" s="1">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A174" s="1">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A175" s="1">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A176" s="1">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A177" s="1">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A178" s="1">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A179" s="1">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A180" s="1">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A181" s="1">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A182" s="1">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A183" s="1">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A184" s="1">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A185" s="1">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A186" s="1">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A187" s="1">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A188" s="1">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A189" s="1">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A190" s="1">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A191" s="1">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A192" s="1">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A193" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A194" s="1">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A195" s="1">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A196" s="1">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A197" s="1">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A198" s="1">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A199" s="1">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A200" s="1">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A201" s="1">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A202" s="1">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A203" s="1">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A204" s="1">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A205" s="1">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A206" s="1">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A207" s="1">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A208" s="1">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A209" s="1">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A210" s="1">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A211" s="1">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A212" s="1">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A213" s="1">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A214" s="1">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A215" s="1">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A216" s="1">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A217" s="1">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A218" s="1">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A219" s="1">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A220" s="1">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A221" s="1">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A222" s="1">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A223" s="1">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A224" s="1">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A225" s="1">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A226" s="1">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A227" s="1">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A228" s="1">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A229" s="1">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A230" s="1">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A231" s="1">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A232" s="1">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A233" s="1">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A234" s="1">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A235" s="1">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A236" s="1">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A237" s="1">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A238" s="1">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A239" s="1">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A240" s="1">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A241" s="1">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A242" s="1">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A243" s="1">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A244" s="1">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A245" s="1">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A246" s="1">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A247" s="1">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A248" s="1">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A249" s="1">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A250" s="1">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A251" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A252" s="1">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A253" s="1">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A254" s="1">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A255" s="1">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A256" s="1">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A257" s="1">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A258" s="1">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A259" s="1">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A260" s="1">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A261" s="1">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A262" s="1">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A263" s="1">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A264" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A265" s="1">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A266" s="1">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A267" s="1">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A268" s="1">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A269" s="1">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A270" s="1">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A271" s="1">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A272" s="1">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A273" s="1">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A274" s="1">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A275" s="1">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A276" s="1">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A277" s="1">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A278" s="1">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A279" s="1">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A280" s="1">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A281" s="1">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A282" s="1">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A283" s="1">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A284" s="1">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A285" s="1">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A286" s="1">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A287" s="1">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A288" s="1">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A289" s="1">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A290" s="1">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A291" s="1">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A292" s="1">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A293" s="1">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A294" s="1">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A295" s="1">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A296" s="1">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A297" s="1">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A298" s="1">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A299" s="1">
+        <v>529</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>